--- a/Assets/Resources/MasterData/FloorData.xlsx
+++ b/Assets/Resources/MasterData/FloorData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39435F12-8244-41F6-A10E-EAF5EC37CE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A56FB06-AC3B-4EEE-94A6-647891E03D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="-15645" windowWidth="12465" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5685" yWindow="-15165" windowWidth="19680" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FloorData" sheetId="1" r:id="rId1"/>
@@ -25,13 +25,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>floorCount</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>spriteIndex</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>enemyTableID</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -380,42 +384,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="10.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
       </c>
+      <c r="C2" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1">
         <v>2</v>
       </c>
     </row>

--- a/Assets/Resources/MasterData/FloorData.xlsx
+++ b/Assets/Resources/MasterData/FloorData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅳ\UnityProject\2DRoguelikeSubject\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A56FB06-AC3B-4EEE-94A6-647891E03D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D22DC4E-2155-4964-9FBF-6C0ED480620D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5685" yWindow="-15165" windowWidth="19680" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FloorData" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>floorCount</t>
     <phoneticPr fontId="1"/>
@@ -36,6 +36,10 @@
   </si>
   <si>
     <t>enemyTableID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>itemTableID</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -384,15 +388,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="10.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -402,8 +407,11 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -413,8 +421,11 @@
       <c r="C2" s="1">
         <v>0</v>
       </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -424,8 +435,11 @@
       <c r="C3" s="1">
         <v>1</v>
       </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -433,6 +447,9 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
+        <v>2</v>
+      </c>
+      <c r="D4" s="1">
         <v>2</v>
       </c>
     </row>
